--- a/public/exports-from-60/29189560.xlsx
+++ b/public/exports-from-60/29189560.xlsx
@@ -59,7 +59,7 @@
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Areal (m²)</t>
+          <t xml:space="preserve">Opvarmet BBR-areal (m²)</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027988</t>
+          <t xml:space="preserve">200027989</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043061</t>
+          <t xml:space="preserve">200043067</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">

--- a/public/exports-from-60/29189560.xlsx
+++ b/public/exports-from-60/29189560.xlsx
@@ -16864,7 +16864,7 @@
       </c>
       <c r="K225" t="inlineStr">
         <is>
-          <t xml:space="preserve">200027989</t>
+          <t xml:space="preserve">200027988</t>
         </is>
       </c>
       <c r="L225" t="inlineStr">
@@ -19864,7 +19864,7 @@
       </c>
       <c r="K265" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L265" t="inlineStr">
@@ -19939,7 +19939,7 @@
       </c>
       <c r="K266" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L266" t="inlineStr">
@@ -20014,7 +20014,7 @@
       </c>
       <c r="K267" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L267" t="inlineStr">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="K268" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L268" t="inlineStr">
@@ -20164,7 +20164,7 @@
       </c>
       <c r="K269" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L269" t="inlineStr">
@@ -20239,7 +20239,7 @@
       </c>
       <c r="K270" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L270" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="K271" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L271" t="inlineStr">
@@ -20389,7 +20389,7 @@
       </c>
       <c r="K272" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L272" t="inlineStr">
@@ -20464,7 +20464,7 @@
       </c>
       <c r="K273" t="inlineStr">
         <is>
-          <t xml:space="preserve">200043067</t>
+          <t xml:space="preserve">200043061</t>
         </is>
       </c>
       <c r="L273" t="inlineStr">
@@ -23689,7 +23689,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23764,7 +23764,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23914,7 +23914,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -23989,7 +23989,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235933</t>
+          <t xml:space="preserve">311235937</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251069</t>
+          <t xml:space="preserve">311251072</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">

--- a/public/exports-from-60/29189560.xlsx
+++ b/public/exports-from-60/29189560.xlsx
@@ -23689,7 +23689,7 @@
       </c>
       <c r="K316" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L316" t="inlineStr">
@@ -23764,7 +23764,7 @@
       </c>
       <c r="K317" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L317" t="inlineStr">
@@ -23839,7 +23839,7 @@
       </c>
       <c r="K318" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L318" t="inlineStr">
@@ -23914,7 +23914,7 @@
       </c>
       <c r="K319" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L319" t="inlineStr">
@@ -23989,7 +23989,7 @@
       </c>
       <c r="K320" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L320" t="inlineStr">
@@ -24064,7 +24064,7 @@
       </c>
       <c r="K321" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L321" t="inlineStr">
@@ -24139,7 +24139,7 @@
       </c>
       <c r="K322" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L322" t="inlineStr">
@@ -24214,7 +24214,7 @@
       </c>
       <c r="K323" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L323" t="inlineStr">
@@ -24289,7 +24289,7 @@
       </c>
       <c r="K324" t="inlineStr">
         <is>
-          <t xml:space="preserve">311235937</t>
+          <t xml:space="preserve">311235933</t>
         </is>
       </c>
       <c r="L324" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="K341" t="inlineStr">
         <is>
-          <t xml:space="preserve">311251072</t>
+          <t xml:space="preserve">311251069</t>
         </is>
       </c>
       <c r="L341" t="inlineStr">
